--- a/tools/importer/reports/import-customer-story-page.report.xlsx
+++ b/tools/importer/reports/import-customer-story-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>customer-story-page</t>
   </si>
   <si>
-    <t>2026-03-16T11:54:49.690Z</t>
+    <t>2026-03-16T12:29:34.829Z</t>
   </si>
   <si>
     <t>McLaren Formula 1® Team | Dell USA</t>
@@ -73,7 +73,7 @@
     <t>ai-solutions-page</t>
   </si>
   <si>
-    <t>2026-03-12T19:57:22.926Z</t>
+    <t>2026-03-16T12:28:46.522Z</t>
   </si>
   <si>
     <t>Artificial Intelligence Solutions | Dell USA</t>

--- a/tools/importer/reports/import-customer-story-page.report.xlsx
+++ b/tools/importer/reports/import-customer-story-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,48 @@
     <t>url</t>
   </si>
   <si>
+    <t>en-us/lp/disaggregated-infrastructure.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/disaggregated-infrastructure</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>solutions-landing-page</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:36.330Z</t>
+  </si>
+  <si>
+    <t>Disaggregated Infrastructure | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/disaggregated-infrastructure</t>
+  </si>
+  <si>
+    <t>en-us/lp/enterprise-upgrades.report.json</t>
+  </si>
+  <si>
+    <t>["cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/enterprise-upgrades</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:51.248Z</t>
+  </si>
+  <si>
+    <t>Dell Technologies - Enterprise Upgrades For Your Server | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/enterprise-upgrades</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/customer-stories-mclaren-racing.report.json</t>
   </si>
   <si>
@@ -46,13 +88,10 @@
     <t>en-us/lp/dt/customer-stories-mclaren-racing</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>customer-story-page</t>
   </si>
   <si>
-    <t>2026-03-16T12:29:34.829Z</t>
+    <t>2026-03-16T13:10:23.041Z</t>
   </si>
   <si>
     <t>McLaren Formula 1® Team | Dell USA</t>
@@ -61,6 +100,45 @@
     <t>https://www.dell.com/en-us/lp/dt/customer-stories-mclaren-racing</t>
   </si>
   <si>
+    <t>en-us/lp/dt/energy-efficient-data-center.report.json</t>
+  </si>
+  <si>
+    <t>["cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/energy-efficient-data-center</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:43.809Z</t>
+  </si>
+  <si>
+    <t>Energy-Efficient Data Center | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/energy-efficient-data-center</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/apex.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","accordion","tabs"]</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/apex</t>
+  </si>
+  <si>
+    <t>product-category-page</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:41.909Z</t>
+  </si>
+  <si>
+    <t>Dell APEX Subscription &amp; as-a-Service Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/scc/sc/apex</t>
+  </si>
+  <si>
     <t>en-us/shop/scc/sc/artificial-intelligence.report.json</t>
   </si>
   <si>
@@ -73,13 +151,103 @@
     <t>ai-solutions-page</t>
   </si>
   <si>
-    <t>2026-03-16T12:28:46.522Z</t>
+    <t>2026-03-16T13:10:09.017Z</t>
   </si>
   <si>
     <t>Artificial Intelligence Solutions | Dell USA</t>
   </si>
   <si>
     <t>https://www.dell.com/en-us/shop/scc/sc/artificial-intelligence</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/cyber-resilience.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","accordion","carousel","tabs"]</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/cyber-resilience</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:09.465Z</t>
+  </si>
+  <si>
+    <t>Cyber Resilience – Data Backup Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/scc/sc/cyber-resilience</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/networking-products.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","accordion","accordion","tabs"]</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/networking-products</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:24.980Z</t>
+  </si>
+  <si>
+    <t>Networking Solutions - Scalable, AI-Ready Infrastructure | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/scc/sc/networking-products</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/private-cloud-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","accordion","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/private-cloud-solutions</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:18.537Z</t>
+  </si>
+  <si>
+    <t>Private Cloud and HCI Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/scc/sc/private-cloud-solutions</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/servers.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","cards","accordion","accordion","carousel","tabs"]</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/servers</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:50.538Z</t>
+  </si>
+  <si>
+    <t>Servers - Rack, Tower &amp; Edge Servers | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/scc/sc/servers</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/storage-products.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","accordion","accordion","carousel","tabs"]</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/storage-products</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:59.006Z</t>
+  </si>
+  <si>
+    <t>Enterprise Data Storage: Cloud, NAS, &amp; Flash Storage | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/scc/sc/storage-products</t>
   </si>
 </sst>
 </file>
@@ -468,15 +636,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="46" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -545,16 +712,250 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-customer-story-page.report.xlsx
+++ b/tools/importer/reports/import-customer-story-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>solutions-landing-page</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:36.330Z</t>
+    <t>2026-03-16T13:22:45.162Z</t>
   </si>
   <si>
     <t>Disaggregated Infrastructure | Dell USA</t>
@@ -70,7 +70,7 @@
     <t>en-us/lp/enterprise-upgrades</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:51.248Z</t>
+    <t>2026-03-16T13:23:01.130Z</t>
   </si>
   <si>
     <t>Dell Technologies - Enterprise Upgrades For Your Server | Dell USA</t>
@@ -91,7 +91,7 @@
     <t>customer-story-page</t>
   </si>
   <si>
-    <t>2026-03-16T13:10:23.041Z</t>
+    <t>2026-03-16T13:23:29.485Z</t>
   </si>
   <si>
     <t>McLaren Formula 1® Team | Dell USA</t>
@@ -100,6 +100,24 @@
     <t>https://www.dell.com/en-us/lp/dt/customer-stories-mclaren-racing</t>
   </si>
   <si>
+    <t>en-us/lp/dt/devops-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["columns","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/devops-solutions</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:22:37.890Z</t>
+  </si>
+  <si>
+    <t>Developers &amp; DevOps | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/devops-solutions</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/energy-efficient-data-center.report.json</t>
   </si>
   <si>
@@ -109,7 +127,7 @@
     <t>en-us/lp/dt/energy-efficient-data-center</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:43.809Z</t>
+    <t>2026-03-16T13:22:52.770Z</t>
   </si>
   <si>
     <t>Energy-Efficient Data Center | Dell USA</t>
@@ -118,6 +136,24 @@
     <t>https://www.dell.com/en-us/lp/dt/energy-efficient-data-center</t>
   </si>
   <si>
+    <t>en-us/lp/dt/payment-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["columns","columns","columns","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/payment-solutions</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:22:31.578Z</t>
+  </si>
+  <si>
+    <t>Payment Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/payment-solutions</t>
+  </si>
+  <si>
     <t>en-us/shop/scc/sc/apex.report.json</t>
   </si>
   <si>
@@ -130,7 +166,7 @@
     <t>product-category-page</t>
   </si>
   <si>
-    <t>2026-03-16T13:08:41.909Z</t>
+    <t>2026-03-16T13:21:39.190Z</t>
   </si>
   <si>
     <t>Dell APEX Subscription &amp; as-a-Service Solutions | Dell USA</t>
@@ -151,7 +187,7 @@
     <t>ai-solutions-page</t>
   </si>
   <si>
-    <t>2026-03-16T13:10:09.017Z</t>
+    <t>2026-03-16T13:23:21.722Z</t>
   </si>
   <si>
     <t>Artificial Intelligence Solutions | Dell USA</t>
@@ -169,7 +205,7 @@
     <t>en-us/shop/scc/sc/cyber-resilience</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:09.465Z</t>
+    <t>2026-03-16T13:22:02.845Z</t>
   </si>
   <si>
     <t>Cyber Resilience – Data Backup Solutions | Dell USA</t>
@@ -187,7 +223,7 @@
     <t>en-us/shop/scc/sc/networking-products</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:24.980Z</t>
+    <t>2026-03-16T13:22:14.986Z</t>
   </si>
   <si>
     <t>Networking Solutions - Scalable, AI-Ready Infrastructure | Dell USA</t>
@@ -205,7 +241,7 @@
     <t>en-us/shop/scc/sc/private-cloud-solutions</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:18.537Z</t>
+    <t>2026-03-16T13:22:08.558Z</t>
   </si>
   <si>
     <t>Private Cloud and HCI Solutions | Dell USA</t>
@@ -223,7 +259,7 @@
     <t>en-us/shop/scc/sc/servers</t>
   </si>
   <si>
-    <t>2026-03-16T13:08:50.538Z</t>
+    <t>2026-03-16T13:21:44.721Z</t>
   </si>
   <si>
     <t>Servers - Rack, Tower &amp; Edge Servers | Dell USA</t>
@@ -241,7 +277,7 @@
     <t>en-us/shop/scc/sc/storage-products</t>
   </si>
   <si>
-    <t>2026-03-16T13:08:59.006Z</t>
+    <t>2026-03-16T13:21:54.440Z</t>
   </si>
   <si>
     <t>Enterprise Data Storage: Cloud, NAS, &amp; Flash Storage | Dell USA</t>
@@ -636,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -790,85 +826,85 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>40</v>
-      </c>
-      <c r="H6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>43</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>45</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>46</v>
-      </c>
-      <c r="G7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>52</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>53</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>56</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
         <v>57</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
@@ -894,7 +930,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
         <v>64</v>
@@ -920,7 +956,7 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
         <v>70</v>
@@ -946,7 +982,7 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
         <v>76</v>
@@ -956,6 +992,58 @@
       </c>
       <c r="H12" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-customer-story-page.report.xlsx
+++ b/tools/importer/reports/import-customer-story-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="566">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,12 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -37,6 +43,51 @@
     <t>url</t>
   </si>
   <si>
+    <t>en-us/lp/dell-experience.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","tabs","carousel","carousel","carousel"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>en-us/lp/dell-experience</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>cp-landing-page</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:58:31.084Z</t>
+  </si>
+  <si>
+    <t>Why Buy Direct from Dell | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dell-experience</t>
+  </si>
+  <si>
+    <t>en-us/lp/dell-video-conferencing-room-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","columns","columns","columns","tabs","tabs","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dell-video-conferencing-room-solutions</t>
+  </si>
+  <si>
+    <t>2026-03-20T17:13:36.771Z</t>
+  </si>
+  <si>
+    <t>Dell Video Conferencing Room Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dell-video-conferencing-room-solutions</t>
+  </si>
+  <si>
     <t>en-us/lp/disaggregated-infrastructure.report.json</t>
   </si>
   <si>
@@ -46,9 +97,6 @@
     <t>en-us/lp/disaggregated-infrastructure</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>solutions-landing-page</t>
   </si>
   <si>
@@ -64,33 +112,612 @@
     <t>en-us/lp/enterprise-upgrades.report.json</t>
   </si>
   <si>
+    <t>["hero","hero","hero","cards","cards","cards","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/enterprise-upgrades</t>
+  </si>
+  <si>
+    <t>2026-03-21T06:41:41.570Z</t>
+  </si>
+  <si>
+    <t>Dell Technologies - Enterprise Upgrades For Your Server | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/enterprise-upgrades</t>
+  </si>
+  <si>
+    <t>en-us/lp/thin-client-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","tabs","tabs","carousel","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/thin-client-solutions</t>
+  </si>
+  <si>
+    <t>2026-03-20T17:13:43.915Z</t>
+  </si>
+  <si>
+    <t>Dell Thin Clients &amp; Secure Cloud Client Workspaces | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/thin-client-solutions</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/artificial-intelligence-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns","cards","cards","cards","carousel","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/artificial-intelligence-services</t>
+  </si>
+  <si>
+    <t>services-detail-page</t>
+  </si>
+  <si>
+    <t>2026-03-21T06:42:35.493Z</t>
+  </si>
+  <si>
+    <t>AI Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/artificial-intelligence-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/automation-platform.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","cards","cards","cards","cards","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/automation-platform</t>
+  </si>
+  <si>
+    <t>2026-03-21T07:53:44.902Z</t>
+  </si>
+  <si>
+    <t>Dell Automation Platform | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/automation-platform</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-airspeeder.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-airspeeder</t>
+  </si>
+  <si>
+    <t>customer-story-page</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:02:13.335Z</t>
+  </si>
+  <si>
+    <t>Airspeeder | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-airspeeder</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-algoma-steel.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-algoma-steel</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:59:29.071Z</t>
+  </si>
+  <si>
+    <t>Algoma Steel | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-algoma-steel</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-aumovio.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-aumovio</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:56:54.169Z</t>
+  </si>
+  <si>
+    <t>AUMOVIO | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-aumovio</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-barkley.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-barkley</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:59:49.126Z</t>
+  </si>
+  <si>
+    <t>Barkley | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-barkley</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-caliber-financial-services.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-caliber-financial-services</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:02:58.240Z</t>
+  </si>
+  <si>
+    <t>Caliber Financial Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-caliber-financial-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-cegal.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-cegal</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:01:18.731Z</t>
+  </si>
+  <si>
+    <t>Cegal | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-cegal</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-city-of-amarillo-genai.report.json</t>
+  </si>
+  <si>
     <t>["cards","cards"]</t>
   </si>
   <si>
-    <t>en-us/lp/enterprise-upgrades</t>
-  </si>
-  <si>
-    <t>2026-03-16T13:23:01.130Z</t>
-  </si>
-  <si>
-    <t>Dell Technologies - Enterprise Upgrades For Your Server | Dell USA</t>
-  </si>
-  <si>
-    <t>https://www.dell.com/en-us/lp/enterprise-upgrades</t>
+    <t>en-us/lp/dt/customer-stories-city-of-amarillo-genai</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:55:10.576Z</t>
+  </si>
+  <si>
+    <t>City of Amarillo​ | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-city-of-amarillo-genai</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-commonwealth-charter-academy.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-commonwealth-charter-academy</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:59:42.309Z</t>
+  </si>
+  <si>
+    <t>Commonwealth Charter Academy | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-commonwealth-charter-academy</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-cosm.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-cosm</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:57:23.100Z</t>
+  </si>
+  <si>
+    <t>Cosm | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-cosm</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-county-of-kauai.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-county-of-kauai</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:01:33.628Z</t>
+  </si>
+  <si>
+    <t>County of Kaua’i | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-county-of-kauai</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-dauntless-xr.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-dauntless-xr</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:56:39.022Z</t>
+  </si>
+  <si>
+    <t>Dauntless XR | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-dauntless-xr</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-deloitte.report.json</t>
+  </si>
+  <si>
+    <t>["cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-deloitte</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:53:05.120Z</t>
+  </si>
+  <si>
+    <t>Deloitte | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-deloitte</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-drogaria-araujo.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-drogaria-araujo</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:56:08.835Z</t>
+  </si>
+  <si>
+    <t>Drogaria Araujo | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-drogaria-araujo</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-eaton.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-eaton</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:01:53.922Z</t>
+  </si>
+  <si>
+    <t>Eaton | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-eaton</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-elice.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-elice</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:57:31.032Z</t>
+  </si>
+  <si>
+    <t>Elice | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-elice</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-emirates-nbd.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-emirates-nbd</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:58:45.289Z</t>
+  </si>
+  <si>
+    <t>Emirates NBD | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-emirates-nbd</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-essen-university-hospital.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-essen-university-hospital</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:58:17.564Z</t>
+  </si>
+  <si>
+    <t>Essen University Hospital | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-essen-university-hospital</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-f1soft-group.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-f1soft-group</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:57:01.985Z</t>
+  </si>
+  <si>
+    <t>F1Soft Group | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-f1soft-group</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-fulgent-technologies.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-fulgent-technologies</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:02:51.405Z</t>
+  </si>
+  <si>
+    <t>Fulgent Genetics | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-fulgent-technologies</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-ghent-university.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-ghent-university</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:59:06.287Z</t>
+  </si>
+  <si>
+    <t>Ghent University | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-ghent-university</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-harbor-solutions.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-harbor-solutions</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:59:35.111Z</t>
+  </si>
+  <si>
+    <t>Harbor | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-harbor-solutions</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-hopeworks.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-hopeworks</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:55:49.146Z</t>
+  </si>
+  <si>
+    <t>Hopeworks | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-hopeworks</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-hopp-childrens-cancer-center-heidelberg-kitz.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-hopp-childrens-cancer-center-heidelberg-kitz</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:55:55.969Z</t>
+  </si>
+  <si>
+    <t>Hopp Children’s Cancer Center Heidelberg (KiTZ) | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-hopp-childrens-cancer-center-heidelberg-kitz</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-hostinger.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-hostinger</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:02:43.231Z</t>
+  </si>
+  <si>
+    <t>Hostinger | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-hostinger</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-instadeep.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-instadeep</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:02:20.345Z</t>
+  </si>
+  <si>
+    <t>InstaDeep | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-instadeep</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-iren.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-iren</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:58:24.780Z</t>
+  </si>
+  <si>
+    <t>IREN | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-iren</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-kennedy-miller-mitchell.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-kennedy-miller-mitchell</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:58:52.698Z</t>
+  </si>
+  <si>
+    <t>Kennedy Miller Mitchell | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-kennedy-miller-mitchell</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-lafayette-utilities-system.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-lafayette-utilities-system</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:58:11.119Z</t>
+  </si>
+  <si>
+    <t>Lafayette Utilities System | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-lafayette-utilities-system</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-lightstormentertainment.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-lightstormentertainment</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:55:20.131Z</t>
+  </si>
+  <si>
+    <t>Lightstorm Entertainment Inc. | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-lightstormentertainment</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-lowes.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-lowes</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:53:57.718Z</t>
+  </si>
+  <si>
+    <t>Lowe's | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-lowes</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-macquarie-cloud-services.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-macquarie-cloud-services</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:55:28.038Z</t>
+  </si>
+  <si>
+    <t>Macquarie Cloud Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-macquarie-cloud-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-maricopa-county-recorders-office.report.json</t>
+  </si>
+  <si>
+    <t>["hero"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-maricopa-county-recorders-office</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:59:00.403Z</t>
+  </si>
+  <si>
+    <t>Customer Stories | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-maricopa-county-recorders-office</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-mark-iii-systems.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-mark-iii-systems</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:58:32.923Z</t>
+  </si>
+  <si>
+    <t>Mark III Systems | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-mark-iii-systems</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-matrixspace.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-matrixspace</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:55:40.595Z</t>
+  </si>
+  <si>
+    <t>MatrixSpace | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-matrixspace</t>
   </si>
   <si>
     <t>en-us/lp/dt/customer-stories-mclaren-racing.report.json</t>
   </si>
   <si>
-    <t>["hero","columns","cards","cards"]</t>
-  </si>
-  <si>
     <t>en-us/lp/dt/customer-stories-mclaren-racing</t>
   </si>
   <si>
-    <t>customer-story-page</t>
-  </si>
-  <si>
     <t>2026-03-16T13:23:29.485Z</t>
   </si>
   <si>
@@ -100,16 +727,538 @@
     <t>https://www.dell.com/en-us/lp/dt/customer-stories-mclaren-racing</t>
   </si>
   <si>
+    <t>en-us/lp/dt/customer-stories-memorial-sloan-kettering-cancer-center.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-memorial-sloan-kettering-cancer-center</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:01:25.950Z</t>
+  </si>
+  <si>
+    <t>Memorial Sloan Kettering Cancer Center | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-memorial-sloan-kettering-cancer-center</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-miami-dolphins.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-miami-dolphins</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:53:12.877Z</t>
+  </si>
+  <si>
+    <t>Miami Dolphins | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-miami-dolphins</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-nature-fresh-farms.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-nature-fresh-farms</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:01:46.608Z</t>
+  </si>
+  <si>
+    <t>Nature Fresh Farms | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-nature-fresh-farms</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-naver-cloud.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-naver-cloud</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:56:46.260Z</t>
+  </si>
+  <si>
+    <t>NAVER Cloud | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-naver-cloud</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-new-belgium-brewing-company.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-new-belgium-brewing-company</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:00:20.277Z</t>
+  </si>
+  <si>
+    <t>New Belgium Brewing Company | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-new-belgium-brewing-company</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-norby.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-norby</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:58:39.091Z</t>
+  </si>
+  <si>
+    <t>Norby | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-norby</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-northwestern-medicine.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","hero","hero","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-northwestern-medicine</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:54:05.727Z</t>
+  </si>
+  <si>
+    <t>Northwestern Medicine | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-northwestern-medicine</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-northwestern-mutual.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-northwestern-mutual</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:53:27.467Z</t>
+  </si>
+  <si>
+    <t>Northwestern Mutual | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-northwestern-mutual</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-nuvance-health.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-nuvance-health</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:00:28.305Z</t>
+  </si>
+  <si>
+    <t>Nuvance Health | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-nuvance-health</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-oregon-state-university.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-oregon-state-university</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:02:28.325Z</t>
+  </si>
+  <si>
+    <t>Oregon State University | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-oregon-state-university</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-palladium-hotel-group.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-palladium-hotel-group</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:02:01.860Z</t>
+  </si>
+  <si>
+    <t>Palladium Hotel Group | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-palladium-hotel-group</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-phonepe.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-phonepe</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:01:12.422Z</t>
+  </si>
+  <si>
+    <t>PhonePe | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-phonepe</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-prime-vision.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-prime-vision</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:58:03.434Z</t>
+  </si>
+  <si>
+    <t>Prime Vision | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-prime-vision</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-psa-corporation.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-psa-corporation</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:01:05.496Z</t>
+  </si>
+  <si>
+    <t>PSA Corporation | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-psa-corporation</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-purdue-university.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-purdue-university</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:53:52.002Z</t>
+  </si>
+  <si>
+    <t>Purdue University | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-purdue-university</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-purehealth.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-purehealth</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:02:35.563Z</t>
+  </si>
+  <si>
+    <t>PureHealth | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-purehealth</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-rakutengroup.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-rakutengroup</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:00:13.062Z</t>
+  </si>
+  <si>
+    <t>Rakuten Group | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-rakutengroup</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-samsung-sds.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-samsung-sds</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:53:43.826Z</t>
+  </si>
+  <si>
+    <t>Samsung SDS | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-samsung-sds</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-sandisk-corporation.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-sandisk-corporation</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:56:32.134Z</t>
+  </si>
+  <si>
+    <t>Sandisk Corporation | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-sandisk-corporation</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-smarsh.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-smarsh</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:57:15.573Z</t>
+  </si>
+  <si>
+    <t>Smarsh | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-smarsh</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-sns-network.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-sns-network</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:01:39.263Z</t>
+  </si>
+  <si>
+    <t>SNS Network | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-sns-network</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-subaru-corporation.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-subaru-corporation</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:53:36.208Z</t>
+  </si>
+  <si>
+    <t>Subaru Corporation | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-subaru-corporation</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-taboola.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-taboola</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:52:56.515Z</t>
+  </si>
+  <si>
+    <t>Taboola | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-taboola</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-team-liquid.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-team-liquid</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:00:04.776Z</t>
+  </si>
+  <si>
+    <t>Team Liquid | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-team-liquid</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-the-avk-group.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-the-avk-group</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:59:24.676Z</t>
+  </si>
+  <si>
+    <t>AVK Holding | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-the-avk-group</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-the-wellcome-sanger-institute.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-the-wellcome-sanger-institute</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:55:34.875Z</t>
+  </si>
+  <si>
+    <t>The Wellcome Sanger Institute | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-the-wellcome-sanger-institute</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-theguthrieclinic.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-theguthrieclinic</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:56:02.209Z</t>
+  </si>
+  <si>
+    <t>The Guthrie Clinic | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-theguthrieclinic</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-university-of-texas-athletics.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-university-of-texas-athletics</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:53:21.234Z</t>
+  </si>
+  <si>
+    <t>University of Texas Athletics | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-university-of-texas-athletics</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-websupport.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-websupport</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:57:39.143Z</t>
+  </si>
+  <si>
+    <t>Websupport | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-websupport</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-worley.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-worley</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:57:08.441Z</t>
+  </si>
+  <si>
+    <t>Worley | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-worley</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-zero.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-zero</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:00:56.994Z</t>
+  </si>
+  <si>
+    <t>ZERO | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-zero</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-zoho-corporation.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-zoho-corporation</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:56:15.205Z</t>
+  </si>
+  <si>
+    <t>Zoho Corporation | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-zoho-corporation</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-zurich-insurance-group-pcaas.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/customer-stories-zurich-insurance-group-pcaas</t>
+  </si>
+  <si>
+    <t>2026-03-21T17:59:56.192Z</t>
+  </si>
+  <si>
+    <t>Zurich Insurance Group | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/customer-stories-zurich-insurance-group-pcaas</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/deployment-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","columns","columns","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/deployment-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:07:01.557Z</t>
+  </si>
+  <si>
+    <t>Deployment Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/deployment-services</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/devops-solutions.report.json</t>
   </si>
   <si>
-    <t>["columns","cards"]</t>
+    <t>["hero","hero","columns","cards","carousel","carousel"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/devops-solutions</t>
   </si>
   <si>
-    <t>2026-03-16T13:22:37.890Z</t>
+    <t>2026-03-21T06:41:52.101Z</t>
   </si>
   <si>
     <t>Developers &amp; DevOps | Dell USA</t>
@@ -121,13 +1270,13 @@
     <t>en-us/lp/dt/energy-efficient-data-center.report.json</t>
   </si>
   <si>
-    <t>["cards"]</t>
+    <t>["hero","cards","cards","carousel"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/energy-efficient-data-center</t>
   </si>
   <si>
-    <t>2026-03-16T13:22:52.770Z</t>
+    <t>2026-03-21T06:41:47.233Z</t>
   </si>
   <si>
     <t>Energy-Efficient Data Center | Dell USA</t>
@@ -136,16 +1285,88 @@
     <t>https://www.dell.com/en-us/lp/dt/energy-efficient-data-center</t>
   </si>
   <si>
+    <t>en-us/lp/dt/lifecycle-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/lifecycle-services</t>
+  </si>
+  <si>
+    <t>services-category-page</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:58:10.789Z</t>
+  </si>
+  <si>
+    <t>Lifecycle Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/lifecycle-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/managed-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","columns","columns","columns","cards","cards","cards","cards","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/managed-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:07:06.968Z</t>
+  </si>
+  <si>
+    <t>Managed Services and Residency Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/managed-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/modern-workforce.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","cards","cards","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/modern-workforce</t>
+  </si>
+  <si>
+    <t>2026-03-21T06:42:30.459Z</t>
+  </si>
+  <si>
+    <t>Modern Workforce Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/modern-workforce</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/multicloud-services.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/multicloud-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:06:40.037Z</t>
+  </si>
+  <si>
+    <t>Multicloud Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/multicloud-services</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/payment-solutions.report.json</t>
   </si>
   <si>
-    <t>["columns","columns","columns","cards","cards"]</t>
+    <t>["hero","columns","columns","columns","cards","cards","carousel","carousel","accordion"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/payment-solutions</t>
   </si>
   <si>
-    <t>2026-03-16T13:22:31.578Z</t>
+    <t>2026-03-21T06:41:59.399Z</t>
   </si>
   <si>
     <t>Payment Solutions | Dell USA</t>
@@ -154,6 +1375,198 @@
     <t>https://www.dell.com/en-us/lp/dt/payment-solutions</t>
   </si>
   <si>
+    <t>en-us/lp/dt/professional-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","carousel","carousel","columns","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/professional-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:04:34.680Z</t>
+  </si>
+  <si>
+    <t>Professional Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/professional-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/recovery-recycling-services.report.json</t>
+  </si>
+  <si>
+    <t>["cards","cards","cards","carousel","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/recovery-recycling-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:07:20.907Z</t>
+  </si>
+  <si>
+    <t>Recovery and Recycling Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/recovery-recycling-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/security-and-resiliency.report.json</t>
+  </si>
+  <si>
+    <t>["cards","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/security-and-resiliency</t>
+  </si>
+  <si>
+    <t>2026-03-21T06:42:24.929Z</t>
+  </si>
+  <si>
+    <t>Security and Resilience Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/security-and-resiliency</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","hero","columns","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/services</t>
+  </si>
+  <si>
+    <t>services-hub-page</t>
+  </si>
+  <si>
+    <t>2026-03-19T23:06:28.738Z</t>
+  </si>
+  <si>
+    <t>View All Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/support-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","columns"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/support-services</t>
+  </si>
+  <si>
+    <t>2026-03-21T06:42:13.426Z</t>
+  </si>
+  <si>
+    <t>Support Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/support-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/technologies-and-tools.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","columns","columns","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/technologies-and-tools</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:06:26.016Z</t>
+  </si>
+  <si>
+    <t>Technologies and Tools | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/technologies-and-tools</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/training-and-certification.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/training-and-certification</t>
+  </si>
+  <si>
+    <t>2026-03-21T06:42:19.064Z</t>
+  </si>
+  <si>
+    <t>Training and Certification | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/training-and-certification</t>
+  </si>
+  <si>
+    <t>en-us/shop/dell-laptops/scr/laptops.report.json</t>
+  </si>
+  <si>
+    <t>en-us/shop/dell-laptops/scr/laptops</t>
+  </si>
+  <si>
+    <t>product-listing-page</t>
+  </si>
+  <si>
+    <t>2026-03-20T17:12:46.418Z</t>
+  </si>
+  <si>
+    <t>Dell Laptops - Shop Work, Gaming &amp; Student PCs | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/dell-laptops/scr/laptops</t>
+  </si>
+  <si>
+    <t>en-us/shop/dell-pro-max-pcs-and-workstations/sc/workstations.report.json</t>
+  </si>
+  <si>
+    <t>en-us/shop/dell-pro-max-pcs-and-workstations/sc/workstations</t>
+  </si>
+  <si>
+    <t>system-category-page</t>
+  </si>
+  <si>
+    <t>2026-03-20T17:13:21.528Z</t>
+  </si>
+  <si>
+    <t>Dell Pro Max PCs and Workstations | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/dell-pro-max-pcs-and-workstations/sc/workstations</t>
+  </si>
+  <si>
+    <t>en-us/shop/desktop-computers/scr/desktops.report.json</t>
+  </si>
+  <si>
+    <t>en-us/shop/desktop-computers/scr/desktops</t>
+  </si>
+  <si>
+    <t>2026-03-20T17:12:56.973Z</t>
+  </si>
+  <si>
+    <t>Dell Desktop Computer- Best Dell PCs &amp; Personal Computers | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/desktop-computers/scr/desktops</t>
+  </si>
+  <si>
+    <t>en-us/shop/gaming-laptops-pcs-and-accessories/sc/game.report.json</t>
+  </si>
+  <si>
+    <t>en-us/shop/gaming-laptops-pcs-and-accessories/sc/game</t>
+  </si>
+  <si>
+    <t>2026-03-20T17:13:12.797Z</t>
+  </si>
+  <si>
+    <t>Dell Gaming Laptops, PCs, &amp; Accessories | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/gaming-laptops-pcs-and-accessories/sc/game</t>
+  </si>
+  <si>
     <t>en-us/shop/scc/sc/apex.report.json</t>
   </si>
   <si>
@@ -178,19 +1591,23 @@
     <t>en-us/shop/scc/sc/artificial-intelligence.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","cards","cards","cards","tabs","tabs","tabs","carousel","accordion"]</t>
+    <t>CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.
+    at processUrl (file:///home/node/.claude/plugins/cache/excat-marketplace/excat/2.1.1/skills/excat-content-import/scripts/run-bulk-import.js:293:13)
+    at runNextTicks (node:internal/process/task_queues:65:5)
+    at process.processImmediate (node:internal/timers:472:9)
+    at async main (file:///home/node/.claude/plugins/cache/excat-marketplace/excat/2.1.1/skills/excat-content-import/scripts/run-bulk-import.js:457:22)</t>
   </si>
   <si>
     <t>en-us/shop/scc/sc/artificial-intelligence</t>
   </si>
   <si>
-    <t>ai-solutions-page</t>
-  </si>
-  <si>
-    <t>2026-03-16T13:23:21.722Z</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence Solutions | Dell USA</t>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-03-16T22:23:09.210Z</t>
   </si>
   <si>
     <t>https://www.dell.com/en-us/shop/scc/sc/artificial-intelligence</t>
@@ -214,16 +1631,28 @@
     <t>https://www.dell.com/en-us/shop/scc/sc/cyber-resilience</t>
   </si>
   <si>
+    <t>en-us/shop/scc/sc/laptops.report.json</t>
+  </si>
+  <si>
+    <t>en-us/shop/scc/sc/laptops</t>
+  </si>
+  <si>
+    <t>2026-03-20T17:12:36.685Z</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/scc/sc/laptops</t>
+  </si>
+  <si>
     <t>en-us/shop/scc/sc/networking-products.report.json</t>
   </si>
   <si>
-    <t>["hero","cards","cards","accordion","accordion","tabs"]</t>
+    <t>["hero","cards","cards","value-pillars","accordion","accordion","tabs"]</t>
   </si>
   <si>
     <t>en-us/shop/scc/sc/networking-products</t>
   </si>
   <si>
-    <t>2026-03-16T13:22:14.986Z</t>
+    <t>2026-03-16T20:19:05.600Z</t>
   </si>
   <si>
     <t>Networking Solutions - Scalable, AI-Ready Infrastructure | Dell USA</t>
@@ -672,17 +2101,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="50" customWidth="1"/>
+    <col min="1" max="5" width="50" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,347 +2135,3279 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
       <c r="H3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
       <c r="H5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
         <v>47</v>
       </c>
-      <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s">
-        <v>52</v>
-      </c>
       <c r="H8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
         <v>58</v>
       </c>
-      <c r="G9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
         <v>71</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
         <v>75</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>50</v>
-      </c>
       <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" t="s">
         <v>76</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>77</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>79</v>
       </c>
       <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
         <v>80</v>
       </c>
-      <c r="C13" t="s">
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" t="s">
         <v>81</v>
       </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="I13" t="s">
         <v>82</v>
       </c>
-      <c r="G13" t="s">
+      <c r="J13" t="s">
         <v>83</v>
       </c>
-      <c r="H13" t="s">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
         <v>85</v>
       </c>
-      <c r="B14" t="s">
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
         <v>86</v>
       </c>
-      <c r="C14" t="s">
+      <c r="I14" t="s">
         <v>87</v>
       </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="J14" t="s">
         <v>88</v>
       </c>
-      <c r="G14" t="s">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>89</v>
       </c>
-      <c r="H14" t="s">
+      <c r="B15" t="s">
         <v>90</v>
       </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" t="s">
+        <v>112</v>
+      </c>
+      <c r="I19" t="s">
+        <v>113</v>
+      </c>
+      <c r="J19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" t="s">
+        <v>123</v>
+      </c>
+      <c r="I21" t="s">
+        <v>124</v>
+      </c>
+      <c r="J21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
+        <v>139</v>
+      </c>
+      <c r="I24" t="s">
+        <v>140</v>
+      </c>
+      <c r="J24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25" t="s">
+        <v>145</v>
+      </c>
+      <c r="J25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" t="s">
+        <v>149</v>
+      </c>
+      <c r="I26" t="s">
+        <v>150</v>
+      </c>
+      <c r="J26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" t="s">
+        <v>154</v>
+      </c>
+      <c r="I27" t="s">
+        <v>155</v>
+      </c>
+      <c r="J27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" t="s">
+        <v>159</v>
+      </c>
+      <c r="I28" t="s">
+        <v>160</v>
+      </c>
+      <c r="J28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>163</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" t="s">
+        <v>164</v>
+      </c>
+      <c r="I29" t="s">
+        <v>165</v>
+      </c>
+      <c r="J29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>167</v>
+      </c>
+      <c r="B30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>168</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>60</v>
+      </c>
+      <c r="H30" t="s">
+        <v>169</v>
+      </c>
+      <c r="I30" t="s">
+        <v>170</v>
+      </c>
+      <c r="J30" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>60</v>
+      </c>
+      <c r="H31" t="s">
+        <v>174</v>
+      </c>
+      <c r="I31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>178</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H32" t="s">
+        <v>179</v>
+      </c>
+      <c r="I32" t="s">
+        <v>180</v>
+      </c>
+      <c r="J32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>183</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>60</v>
+      </c>
+      <c r="H33" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" t="s">
+        <v>185</v>
+      </c>
+      <c r="J33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>187</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>60</v>
+      </c>
+      <c r="H34" t="s">
+        <v>189</v>
+      </c>
+      <c r="I34" t="s">
+        <v>190</v>
+      </c>
+      <c r="J34" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>192</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>193</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" t="s">
+        <v>194</v>
+      </c>
+      <c r="I35" t="s">
+        <v>195</v>
+      </c>
+      <c r="J35" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>197</v>
+      </c>
+      <c r="B36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
+        <v>198</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36" t="s">
+        <v>199</v>
+      </c>
+      <c r="I36" t="s">
+        <v>200</v>
+      </c>
+      <c r="J36" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>202</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>203</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>60</v>
+      </c>
+      <c r="H37" t="s">
+        <v>204</v>
+      </c>
+      <c r="I37" t="s">
+        <v>205</v>
+      </c>
+      <c r="J37" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>208</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38" t="s">
+        <v>209</v>
+      </c>
+      <c r="I38" t="s">
+        <v>210</v>
+      </c>
+      <c r="J38" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>212</v>
+      </c>
+      <c r="B39" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>213</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>60</v>
+      </c>
+      <c r="H39" t="s">
+        <v>214</v>
+      </c>
+      <c r="I39" t="s">
+        <v>215</v>
+      </c>
+      <c r="J39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>217</v>
+      </c>
+      <c r="B40" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>219</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>60</v>
+      </c>
+      <c r="H40" t="s">
+        <v>220</v>
+      </c>
+      <c r="I40" t="s">
+        <v>221</v>
+      </c>
+      <c r="J40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>224</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>60</v>
+      </c>
+      <c r="H41" t="s">
+        <v>225</v>
+      </c>
+      <c r="I41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J41" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>228</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>229</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>60</v>
+      </c>
+      <c r="H42" t="s">
+        <v>230</v>
+      </c>
+      <c r="I42" t="s">
+        <v>231</v>
+      </c>
+      <c r="J42" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>233</v>
+      </c>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>234</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>60</v>
+      </c>
+      <c r="H43" t="s">
+        <v>235</v>
+      </c>
+      <c r="I43" t="s">
+        <v>236</v>
+      </c>
+      <c r="J43" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>238</v>
+      </c>
+      <c r="B44" t="s">
+        <v>239</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>240</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>60</v>
+      </c>
+      <c r="H44" t="s">
+        <v>241</v>
+      </c>
+      <c r="I44" t="s">
+        <v>242</v>
+      </c>
+      <c r="J44" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>244</v>
+      </c>
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>245</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>60</v>
+      </c>
+      <c r="H45" t="s">
+        <v>246</v>
+      </c>
+      <c r="I45" t="s">
+        <v>247</v>
+      </c>
+      <c r="J45" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>249</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>250</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>60</v>
+      </c>
+      <c r="H46" t="s">
+        <v>251</v>
+      </c>
+      <c r="I46" t="s">
+        <v>252</v>
+      </c>
+      <c r="J46" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>254</v>
+      </c>
+      <c r="B47" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>255</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>60</v>
+      </c>
+      <c r="H47" t="s">
+        <v>256</v>
+      </c>
+      <c r="I47" t="s">
+        <v>257</v>
+      </c>
+      <c r="J47" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>259</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>260</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>60</v>
+      </c>
+      <c r="H48" t="s">
+        <v>261</v>
+      </c>
+      <c r="I48" t="s">
+        <v>262</v>
+      </c>
+      <c r="J48" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>264</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>265</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>60</v>
+      </c>
+      <c r="H49" t="s">
+        <v>266</v>
+      </c>
+      <c r="I49" t="s">
+        <v>267</v>
+      </c>
+      <c r="J49" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>269</v>
+      </c>
+      <c r="B50" t="s">
+        <v>270</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>271</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H50" t="s">
+        <v>272</v>
+      </c>
+      <c r="I50" t="s">
+        <v>273</v>
+      </c>
+      <c r="J50" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>275</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>276</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H51" t="s">
+        <v>277</v>
+      </c>
+      <c r="I51" t="s">
+        <v>278</v>
+      </c>
+      <c r="J51" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>280</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>281</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>60</v>
+      </c>
+      <c r="H52" t="s">
+        <v>282</v>
+      </c>
+      <c r="I52" t="s">
+        <v>283</v>
+      </c>
+      <c r="J52" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>285</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>286</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>60</v>
+      </c>
+      <c r="H53" t="s">
+        <v>287</v>
+      </c>
+      <c r="I53" t="s">
+        <v>288</v>
+      </c>
+      <c r="J53" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>290</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>291</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>60</v>
+      </c>
+      <c r="H54" t="s">
+        <v>292</v>
+      </c>
+      <c r="I54" t="s">
+        <v>293</v>
+      </c>
+      <c r="J54" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>295</v>
+      </c>
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>296</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>60</v>
+      </c>
+      <c r="H55" t="s">
+        <v>297</v>
+      </c>
+      <c r="I55" t="s">
+        <v>298</v>
+      </c>
+      <c r="J55" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>300</v>
+      </c>
+      <c r="B56" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" t="s">
+        <v>301</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>60</v>
+      </c>
+      <c r="H56" t="s">
+        <v>302</v>
+      </c>
+      <c r="I56" t="s">
+        <v>303</v>
+      </c>
+      <c r="J56" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>305</v>
+      </c>
+      <c r="B57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" t="s">
+        <v>306</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>60</v>
+      </c>
+      <c r="H57" t="s">
+        <v>307</v>
+      </c>
+      <c r="I57" t="s">
+        <v>308</v>
+      </c>
+      <c r="J57" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>310</v>
+      </c>
+      <c r="B58" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>311</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>60</v>
+      </c>
+      <c r="H58" t="s">
+        <v>312</v>
+      </c>
+      <c r="I58" t="s">
+        <v>313</v>
+      </c>
+      <c r="J58" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>315</v>
+      </c>
+      <c r="B59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>316</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>60</v>
+      </c>
+      <c r="H59" t="s">
+        <v>317</v>
+      </c>
+      <c r="I59" t="s">
+        <v>318</v>
+      </c>
+      <c r="J59" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>320</v>
+      </c>
+      <c r="B60" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>321</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>60</v>
+      </c>
+      <c r="H60" t="s">
+        <v>322</v>
+      </c>
+      <c r="I60" t="s">
+        <v>323</v>
+      </c>
+      <c r="J60" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>325</v>
+      </c>
+      <c r="B61" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>326</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>60</v>
+      </c>
+      <c r="H61" t="s">
+        <v>327</v>
+      </c>
+      <c r="I61" t="s">
+        <v>328</v>
+      </c>
+      <c r="J61" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>330</v>
+      </c>
+      <c r="B62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>331</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>60</v>
+      </c>
+      <c r="H62" t="s">
+        <v>332</v>
+      </c>
+      <c r="I62" t="s">
+        <v>333</v>
+      </c>
+      <c r="J62" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>335</v>
+      </c>
+      <c r="B63" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>336</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" t="s">
+        <v>60</v>
+      </c>
+      <c r="H63" t="s">
+        <v>337</v>
+      </c>
+      <c r="I63" t="s">
+        <v>338</v>
+      </c>
+      <c r="J63" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>340</v>
+      </c>
+      <c r="B64" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>341</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
+        <v>60</v>
+      </c>
+      <c r="H64" t="s">
+        <v>342</v>
+      </c>
+      <c r="I64" t="s">
+        <v>343</v>
+      </c>
+      <c r="J64" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>345</v>
+      </c>
+      <c r="B65" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>346</v>
+      </c>
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" t="s">
+        <v>60</v>
+      </c>
+      <c r="H65" t="s">
+        <v>347</v>
+      </c>
+      <c r="I65" t="s">
+        <v>348</v>
+      </c>
+      <c r="J65" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>350</v>
+      </c>
+      <c r="B66" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" t="s">
+        <v>351</v>
+      </c>
+      <c r="F66" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" t="s">
+        <v>60</v>
+      </c>
+      <c r="H66" t="s">
+        <v>352</v>
+      </c>
+      <c r="I66" t="s">
+        <v>353</v>
+      </c>
+      <c r="J66" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>355</v>
+      </c>
+      <c r="B67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>356</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" t="s">
+        <v>60</v>
+      </c>
+      <c r="H67" t="s">
+        <v>357</v>
+      </c>
+      <c r="I67" t="s">
+        <v>358</v>
+      </c>
+      <c r="J67" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>360</v>
+      </c>
+      <c r="B68" t="s">
+        <v>239</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" t="s">
+        <v>361</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" t="s">
+        <v>60</v>
+      </c>
+      <c r="H68" t="s">
+        <v>362</v>
+      </c>
+      <c r="I68" t="s">
+        <v>363</v>
+      </c>
+      <c r="J68" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>365</v>
+      </c>
+      <c r="B69" t="s">
+        <v>116</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" t="s">
+        <v>366</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" t="s">
+        <v>60</v>
+      </c>
+      <c r="H69" t="s">
+        <v>367</v>
+      </c>
+      <c r="I69" t="s">
+        <v>368</v>
+      </c>
+      <c r="J69" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>370</v>
+      </c>
+      <c r="B70" t="s">
+        <v>371</v>
+      </c>
+      <c r="C70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" t="s">
+        <v>372</v>
+      </c>
+      <c r="F70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" t="s">
+        <v>60</v>
+      </c>
+      <c r="H70" t="s">
+        <v>373</v>
+      </c>
+      <c r="I70" t="s">
+        <v>374</v>
+      </c>
+      <c r="J70" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>376</v>
+      </c>
+      <c r="B71" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" t="s">
+        <v>377</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" t="s">
+        <v>60</v>
+      </c>
+      <c r="H71" t="s">
+        <v>378</v>
+      </c>
+      <c r="I71" t="s">
+        <v>379</v>
+      </c>
+      <c r="J71" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>381</v>
+      </c>
+      <c r="B72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" t="s">
+        <v>382</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" t="s">
+        <v>60</v>
+      </c>
+      <c r="H72" t="s">
+        <v>383</v>
+      </c>
+      <c r="I72" t="s">
+        <v>384</v>
+      </c>
+      <c r="J72" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>386</v>
+      </c>
+      <c r="B73" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" t="s">
+        <v>387</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s">
+        <v>60</v>
+      </c>
+      <c r="H73" t="s">
+        <v>388</v>
+      </c>
+      <c r="I73" t="s">
+        <v>389</v>
+      </c>
+      <c r="J73" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>391</v>
+      </c>
+      <c r="B74" t="s">
+        <v>58</v>
+      </c>
+      <c r="C74" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" t="s">
+        <v>392</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" t="s">
+        <v>60</v>
+      </c>
+      <c r="H74" t="s">
+        <v>393</v>
+      </c>
+      <c r="I74" t="s">
+        <v>394</v>
+      </c>
+      <c r="J74" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>396</v>
+      </c>
+      <c r="B75" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" t="s">
+        <v>397</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" t="s">
+        <v>60</v>
+      </c>
+      <c r="H75" t="s">
+        <v>398</v>
+      </c>
+      <c r="I75" t="s">
+        <v>399</v>
+      </c>
+      <c r="J75" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>401</v>
+      </c>
+      <c r="B76" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" t="s">
+        <v>402</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" t="s">
+        <v>60</v>
+      </c>
+      <c r="H76" t="s">
+        <v>403</v>
+      </c>
+      <c r="I76" t="s">
+        <v>404</v>
+      </c>
+      <c r="J76" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>406</v>
+      </c>
+      <c r="B77" t="s">
+        <v>407</v>
+      </c>
+      <c r="C77" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" t="s">
+        <v>408</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>47</v>
+      </c>
+      <c r="H77" t="s">
+        <v>409</v>
+      </c>
+      <c r="I77" t="s">
+        <v>410</v>
+      </c>
+      <c r="J77" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>412</v>
+      </c>
+      <c r="B78" t="s">
+        <v>413</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>414</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>28</v>
+      </c>
+      <c r="H78" t="s">
+        <v>415</v>
+      </c>
+      <c r="I78" t="s">
+        <v>416</v>
+      </c>
+      <c r="J78" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>418</v>
+      </c>
+      <c r="B79" t="s">
+        <v>419</v>
+      </c>
+      <c r="C79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" t="s">
+        <v>420</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>28</v>
+      </c>
+      <c r="H79" t="s">
+        <v>421</v>
+      </c>
+      <c r="I79" t="s">
+        <v>422</v>
+      </c>
+      <c r="J79" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>424</v>
+      </c>
+      <c r="B80" t="s">
+        <v>425</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" t="s">
+        <v>426</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>427</v>
+      </c>
+      <c r="H80" t="s">
+        <v>428</v>
+      </c>
+      <c r="I80" t="s">
+        <v>429</v>
+      </c>
+      <c r="J80" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>431</v>
+      </c>
+      <c r="B81" t="s">
+        <v>432</v>
+      </c>
+      <c r="C81" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F81" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s">
+        <v>47</v>
+      </c>
+      <c r="H81" t="s">
+        <v>434</v>
+      </c>
+      <c r="I81" t="s">
+        <v>435</v>
+      </c>
+      <c r="J81" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>437</v>
+      </c>
+      <c r="B82" t="s">
+        <v>438</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" t="s">
+        <v>439</v>
+      </c>
+      <c r="F82" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" t="s">
+        <v>47</v>
+      </c>
+      <c r="H82" t="s">
+        <v>440</v>
+      </c>
+      <c r="I82" t="s">
+        <v>441</v>
+      </c>
+      <c r="J82" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>443</v>
+      </c>
+      <c r="B83" t="s">
+        <v>432</v>
+      </c>
+      <c r="C83" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" t="s">
+        <v>444</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>47</v>
+      </c>
+      <c r="H83" t="s">
+        <v>445</v>
+      </c>
+      <c r="I83" t="s">
+        <v>446</v>
+      </c>
+      <c r="J83" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>448</v>
+      </c>
+      <c r="B84" t="s">
+        <v>449</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" t="s">
+        <v>450</v>
+      </c>
+      <c r="F84" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" t="s">
+        <v>28</v>
+      </c>
+      <c r="H84" t="s">
+        <v>451</v>
+      </c>
+      <c r="I84" t="s">
+        <v>452</v>
+      </c>
+      <c r="J84" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>454</v>
+      </c>
+      <c r="B85" t="s">
+        <v>455</v>
+      </c>
+      <c r="C85" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" t="s">
+        <v>456</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
+        <v>427</v>
+      </c>
+      <c r="H85" t="s">
+        <v>457</v>
+      </c>
+      <c r="I85" t="s">
+        <v>458</v>
+      </c>
+      <c r="J85" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>460</v>
+      </c>
+      <c r="B86" t="s">
+        <v>461</v>
+      </c>
+      <c r="C86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" t="s">
+        <v>462</v>
+      </c>
+      <c r="F86" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" t="s">
+        <v>47</v>
+      </c>
+      <c r="H86" t="s">
+        <v>463</v>
+      </c>
+      <c r="I86" t="s">
+        <v>464</v>
+      </c>
+      <c r="J86" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>466</v>
+      </c>
+      <c r="B87" t="s">
+        <v>467</v>
+      </c>
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" t="s">
+        <v>468</v>
+      </c>
+      <c r="F87" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" t="s">
+        <v>47</v>
+      </c>
+      <c r="H87" t="s">
+        <v>469</v>
+      </c>
+      <c r="I87" t="s">
+        <v>470</v>
+      </c>
+      <c r="J87" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>472</v>
+      </c>
+      <c r="B88" t="s">
+        <v>473</v>
+      </c>
+      <c r="C88" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" t="s">
+        <v>474</v>
+      </c>
+      <c r="F88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" t="s">
+        <v>475</v>
+      </c>
+      <c r="H88" t="s">
+        <v>476</v>
+      </c>
+      <c r="I88" t="s">
+        <v>477</v>
+      </c>
+      <c r="J88" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>479</v>
+      </c>
+      <c r="B89" t="s">
+        <v>480</v>
+      </c>
+      <c r="C89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" t="s">
+        <v>481</v>
+      </c>
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" t="s">
+        <v>47</v>
+      </c>
+      <c r="H89" t="s">
+        <v>482</v>
+      </c>
+      <c r="I89" t="s">
+        <v>483</v>
+      </c>
+      <c r="J89" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>485</v>
+      </c>
+      <c r="B90" t="s">
+        <v>486</v>
+      </c>
+      <c r="C90" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" t="s">
+        <v>487</v>
+      </c>
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" t="s">
+        <v>47</v>
+      </c>
+      <c r="H90" t="s">
+        <v>488</v>
+      </c>
+      <c r="I90" t="s">
+        <v>489</v>
+      </c>
+      <c r="J90" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>491</v>
+      </c>
+      <c r="B91" t="s">
+        <v>137</v>
+      </c>
+      <c r="C91" t="s">
+        <v>12</v>
+      </c>
+      <c r="D91" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" t="s">
+        <v>492</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" t="s">
+        <v>47</v>
+      </c>
+      <c r="H91" t="s">
+        <v>493</v>
+      </c>
+      <c r="I91" t="s">
+        <v>494</v>
+      </c>
+      <c r="J91" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>496</v>
+      </c>
+      <c r="B92" t="s">
+        <v>218</v>
+      </c>
+      <c r="C92" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92" t="s">
+        <v>497</v>
+      </c>
+      <c r="F92" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" t="s">
+        <v>498</v>
+      </c>
+      <c r="H92" t="s">
+        <v>499</v>
+      </c>
+      <c r="I92" t="s">
+        <v>500</v>
+      </c>
+      <c r="J92" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>502</v>
+      </c>
+      <c r="B93" t="s">
+        <v>371</v>
+      </c>
+      <c r="C93" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93" t="s">
+        <v>503</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" t="s">
+        <v>504</v>
+      </c>
+      <c r="H93" t="s">
+        <v>505</v>
+      </c>
+      <c r="I93" t="s">
+        <v>506</v>
+      </c>
+      <c r="J93" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>508</v>
+      </c>
+      <c r="B94" t="s">
+        <v>218</v>
+      </c>
+      <c r="C94" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94" t="s">
+        <v>509</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" t="s">
+        <v>498</v>
+      </c>
+      <c r="H94" t="s">
+        <v>510</v>
+      </c>
+      <c r="I94" t="s">
+        <v>511</v>
+      </c>
+      <c r="J94" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>513</v>
+      </c>
+      <c r="B95" t="s">
+        <v>371</v>
+      </c>
+      <c r="C95" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" t="s">
+        <v>514</v>
+      </c>
+      <c r="F95" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" t="s">
+        <v>504</v>
+      </c>
+      <c r="H95" t="s">
+        <v>515</v>
+      </c>
+      <c r="I95" t="s">
+        <v>516</v>
+      </c>
+      <c r="J95" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>518</v>
+      </c>
+      <c r="B96" t="s">
+        <v>519</v>
+      </c>
+      <c r="C96" t="s">
+        <v>12</v>
+      </c>
+      <c r="D96" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" t="s">
+        <v>520</v>
+      </c>
+      <c r="F96" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" t="s">
+        <v>521</v>
+      </c>
+      <c r="H96" t="s">
+        <v>522</v>
+      </c>
+      <c r="I96" t="s">
+        <v>523</v>
+      </c>
+      <c r="J96" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>525</v>
+      </c>
+      <c r="B97" t="s">
+        <v>12</v>
+      </c>
+      <c r="C97" t="s">
+        <v>526</v>
+      </c>
+      <c r="D97" t="s">
+        <v>527</v>
+      </c>
+      <c r="E97" t="s">
+        <v>528</v>
+      </c>
+      <c r="F97" t="s">
+        <v>529</v>
+      </c>
+      <c r="G97" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" t="s">
+        <v>530</v>
+      </c>
+      <c r="I97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J97" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>532</v>
+      </c>
+      <c r="B98" t="s">
+        <v>533</v>
+      </c>
+      <c r="C98" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" t="s">
+        <v>534</v>
+      </c>
+      <c r="F98" t="s">
+        <v>14</v>
+      </c>
+      <c r="G98" t="s">
+        <v>521</v>
+      </c>
+      <c r="H98" t="s">
+        <v>535</v>
+      </c>
+      <c r="I98" t="s">
+        <v>536</v>
+      </c>
+      <c r="J98" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>538</v>
+      </c>
+      <c r="B99" t="s">
+        <v>218</v>
+      </c>
+      <c r="C99" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" t="s">
+        <v>539</v>
+      </c>
+      <c r="F99" t="s">
+        <v>14</v>
+      </c>
+      <c r="G99" t="s">
+        <v>498</v>
+      </c>
+      <c r="H99" t="s">
+        <v>540</v>
+      </c>
+      <c r="I99" t="s">
+        <v>500</v>
+      </c>
+      <c r="J99" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>542</v>
+      </c>
+      <c r="B100" t="s">
+        <v>543</v>
+      </c>
+      <c r="C100" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" t="s">
+        <v>544</v>
+      </c>
+      <c r="F100" t="s">
+        <v>14</v>
+      </c>
+      <c r="G100" t="s">
+        <v>521</v>
+      </c>
+      <c r="H100" t="s">
+        <v>545</v>
+      </c>
+      <c r="I100" t="s">
+        <v>546</v>
+      </c>
+      <c r="J100" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>548</v>
+      </c>
+      <c r="B101" t="s">
+        <v>549</v>
+      </c>
+      <c r="C101" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" t="s">
+        <v>550</v>
+      </c>
+      <c r="F101" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101" t="s">
+        <v>521</v>
+      </c>
+      <c r="H101" t="s">
+        <v>551</v>
+      </c>
+      <c r="I101" t="s">
+        <v>552</v>
+      </c>
+      <c r="J101" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>554</v>
+      </c>
+      <c r="B102" t="s">
+        <v>555</v>
+      </c>
+      <c r="C102" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102" t="s">
+        <v>556</v>
+      </c>
+      <c r="F102" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" t="s">
+        <v>521</v>
+      </c>
+      <c r="H102" t="s">
+        <v>557</v>
+      </c>
+      <c r="I102" t="s">
+        <v>558</v>
+      </c>
+      <c r="J102" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>560</v>
+      </c>
+      <c r="B103" t="s">
+        <v>561</v>
+      </c>
+      <c r="C103" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" t="s">
+        <v>562</v>
+      </c>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" t="s">
+        <v>521</v>
+      </c>
+      <c r="H103" t="s">
+        <v>563</v>
+      </c>
+      <c r="I103" t="s">
+        <v>564</v>
+      </c>
+      <c r="J103" t="s">
+        <v>565</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-customer-story-page.report.xlsx
+++ b/tools/importer/reports/import-customer-story-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="644">
   <si>
     <t>_reportFile</t>
   </si>
@@ -283,13 +283,13 @@
     <t>en-us/lp/dt/customer-stories-city-of-amarillo-genai.report.json</t>
   </si>
   <si>
-    <t>["cards","cards"]</t>
+    <t>["hero","columns","columns","cards","cards","cards","cards","cards"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/customer-stories-city-of-amarillo-genai</t>
   </si>
   <si>
-    <t>2026-03-21T17:55:10.576Z</t>
+    <t>2026-03-22T03:15:21.992Z</t>
   </si>
   <si>
     <t>City of Amarillo​ | Dell USA</t>
@@ -349,7 +349,7 @@
     <t>en-us/lp/dt/customer-stories-dauntless-xr</t>
   </si>
   <si>
-    <t>2026-03-21T17:56:39.022Z</t>
+    <t>2026-03-22T03:15:29.733Z</t>
   </si>
   <si>
     <t>Dauntless XR | Dell USA</t>
@@ -361,13 +361,13 @@
     <t>en-us/lp/dt/customer-stories-deloitte.report.json</t>
   </si>
   <si>
-    <t>["cards"]</t>
+    <t>["hero","hero","columns","columns","cards","cards","cards","cards"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/customer-stories-deloitte</t>
   </si>
   <si>
-    <t>2026-03-21T17:53:05.120Z</t>
+    <t>2026-03-22T03:14:39.485Z</t>
   </si>
   <si>
     <t>Deloitte | Dell USA</t>
@@ -397,7 +397,7 @@
     <t>en-us/lp/dt/customer-stories-eaton</t>
   </si>
   <si>
-    <t>2026-03-21T18:01:53.922Z</t>
+    <t>2026-03-22T03:14:46.486Z</t>
   </si>
   <si>
     <t>Eaton | Dell USA</t>
@@ -460,7 +460,7 @@
     <t>en-us/lp/dt/customer-stories-f1soft-group</t>
   </si>
   <si>
-    <t>2026-03-21T17:57:01.985Z</t>
+    <t>2026-03-22T03:15:37.318Z</t>
   </si>
   <si>
     <t>F1Soft Group | Dell USA</t>
@@ -517,10 +517,13 @@
     <t>en-us/lp/dt/customer-stories-hopeworks.report.json</t>
   </si>
   <si>
+    <t>["hero","columns","columns","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/customer-stories-hopeworks</t>
   </si>
   <si>
-    <t>2026-03-21T17:55:49.146Z</t>
+    <t>2026-03-22T03:14:53.746Z</t>
   </si>
   <si>
     <t>Hopeworks | Dell USA</t>
@@ -640,7 +643,7 @@
     <t>en-us/lp/dt/customer-stories-lowes</t>
   </si>
   <si>
-    <t>2026-03-21T17:53:57.718Z</t>
+    <t>2026-03-22T03:15:00.681Z</t>
   </si>
   <si>
     <t>Lowe's | Dell USA</t>
@@ -655,7 +658,7 @@
     <t>en-us/lp/dt/customer-stories-macquarie-cloud-services</t>
   </si>
   <si>
-    <t>2026-03-21T17:55:28.038Z</t>
+    <t>2026-03-22T03:15:07.400Z</t>
   </si>
   <si>
     <t>Macquarie Cloud Services | Dell USA</t>
@@ -673,7 +676,7 @@
     <t>en-us/lp/dt/customer-stories-maricopa-county-recorders-office</t>
   </si>
   <si>
-    <t>2026-03-21T17:59:00.403Z</t>
+    <t>2026-03-22T03:16:27.935Z</t>
   </si>
   <si>
     <t>Customer Stories | Dell USA</t>
@@ -781,7 +784,7 @@
     <t>en-us/lp/dt/customer-stories-naver-cloud</t>
   </si>
   <si>
-    <t>2026-03-21T17:56:46.260Z</t>
+    <t>2026-03-22T03:15:45.409Z</t>
   </si>
   <si>
     <t>NAVER Cloud | Dell USA</t>
@@ -889,7 +892,7 @@
     <t>en-us/lp/dt/customer-stories-palladium-hotel-group</t>
   </si>
   <si>
-    <t>2026-03-21T18:02:01.860Z</t>
+    <t>2026-03-22T03:15:14.606Z</t>
   </si>
   <si>
     <t>Palladium Hotel Group | Dell USA</t>
@@ -1009,7 +1012,7 @@
     <t>en-us/lp/dt/customer-stories-sandisk-corporation</t>
   </si>
   <si>
-    <t>2026-03-21T17:56:32.134Z</t>
+    <t>2026-03-22T03:15:52.400Z</t>
   </si>
   <si>
     <t>Sandisk Corporation | Dell USA</t>
@@ -1039,7 +1042,7 @@
     <t>en-us/lp/dt/customer-stories-sns-network</t>
   </si>
   <si>
-    <t>2026-03-21T18:01:39.263Z</t>
+    <t>2026-03-22T03:15:58.105Z</t>
   </si>
   <si>
     <t>SNS Network | Dell USA</t>
@@ -1111,10 +1114,13 @@
     <t>en-us/lp/dt/customer-stories-the-wellcome-sanger-institute.report.json</t>
   </si>
   <si>
+    <t>["hero","hero","columns","columns","cards","cards"]</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/customer-stories-the-wellcome-sanger-institute</t>
   </si>
   <si>
-    <t>2026-03-21T17:55:34.875Z</t>
+    <t>2026-03-22T03:16:04.708Z</t>
   </si>
   <si>
     <t>The Wellcome Sanger Institute | Dell USA</t>
@@ -1132,7 +1138,7 @@
     <t>en-us/lp/dt/customer-stories-theguthrieclinic</t>
   </si>
   <si>
-    <t>2026-03-21T17:56:02.209Z</t>
+    <t>2026-03-22T03:16:19.503Z</t>
   </si>
   <si>
     <t>The Guthrie Clinic | Dell USA</t>
@@ -1147,7 +1153,7 @@
     <t>en-us/lp/dt/customer-stories-university-of-texas-athletics</t>
   </si>
   <si>
-    <t>2026-03-21T17:53:21.234Z</t>
+    <t>2026-03-22T03:16:12.143Z</t>
   </si>
   <si>
     <t>University of Texas Athletics | Dell USA</t>
@@ -1283,6 +1289,234 @@
   </si>
   <si>
     <t>https://www.dell.com/en-us/lp/dt/energy-efficient-data-center</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-energy.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","hero","hero","carousel","carousel","carousel","carousel","cards","cards","cards","cards","cards","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-energy</t>
+  </si>
+  <si>
+    <t>industry-page</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:06:33.359Z</t>
+  </si>
+  <si>
+    <t>Energy | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-energy</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-federal-government-it.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-federal-government-it</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:06:41.600Z</t>
+  </si>
+  <si>
+    <t>Dell Technologies Federal​ | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-federal-government-it</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-financial-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","carousel","carousel","carousel","carousel","cards","cards","cards","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-financial-services</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:06:48.571Z</t>
+  </si>
+  <si>
+    <t>Transforming the Financial Services Industry | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-financial-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-healthcare.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","hero","hero","carousel","carousel","carousel","carousel","cards","cards","cards","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-healthcare</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:06:24.998Z</t>
+  </si>
+  <si>
+    <t>Healthcare | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-healthcare</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-higher-ed.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","hero","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-higher-ed</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:06:57.300Z</t>
+  </si>
+  <si>
+    <t>Higher Education IT Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-higher-ed</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-k12-ed.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-k12-ed</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:07:04.209Z</t>
+  </si>
+  <si>
+    <t>K-12 IT Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-k12-ed</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-life-sciences.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","carousel","carousel","carousel","carousel","cards","cards","cards","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-life-sciences</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:07:11.620Z</t>
+  </si>
+  <si>
+    <t>Life Sciences | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-life-sciences</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-manufacturing.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-manufacturing</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:07:19.816Z</t>
+  </si>
+  <si>
+    <t>Manufacturing | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-manufacturing</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-retail.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-retail</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:07:28.145Z</t>
+  </si>
+  <si>
+    <t>Retail | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-retail</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-safety-security.report.json</t>
+  </si>
+  <si>
+    <t>["cards","cards","cards","columns","columns","columns"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-safety-security</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:07:35.394Z</t>
+  </si>
+  <si>
+    <t>Safety &amp; Security Solutions - Video Storage Analytics | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-safety-security</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-smart-cities.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","cards","columns","accordion","accordion"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-smart-cities</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:07:42.865Z</t>
+  </si>
+  <si>
+    <t>Defining the digital future of our cities | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-smart-cities</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-state-and-local-government.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","hero","carousel","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-state-and-local-government</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:07:50.845Z</t>
+  </si>
+  <si>
+    <t>State and Local Government | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-state-and-local-government</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-telecom.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","hero","hero","hero","cards","cards","cards","cards","cards","cards","columns","columns","columns"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/industry-telecom</t>
+  </si>
+  <si>
+    <t>2026-03-21T18:07:57.086Z</t>
+  </si>
+  <si>
+    <t>Telecom Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/industry-telecom</t>
   </si>
   <si>
     <t>en-us/lp/dt/lifecycle-services.report.json</t>
@@ -2101,7 +2335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -3043,7 +3277,7 @@
         <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -3052,7 +3286,7 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
@@ -3061,18 +3295,18 @@
         <v>60</v>
       </c>
       <c r="H30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s">
         <v>58</v>
@@ -3084,7 +3318,7 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
@@ -3093,18 +3327,18 @@
         <v>60</v>
       </c>
       <c r="H31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B32" t="s">
         <v>58</v>
@@ -3116,7 +3350,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
@@ -3125,18 +3359,18 @@
         <v>60</v>
       </c>
       <c r="H32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -3148,7 +3382,7 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
@@ -3157,18 +3391,18 @@
         <v>60</v>
       </c>
       <c r="H33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s">
         <v>58</v>
@@ -3180,7 +3414,7 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
@@ -3189,18 +3423,18 @@
         <v>60</v>
       </c>
       <c r="H34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
         <v>58</v>
@@ -3212,7 +3446,7 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
@@ -3221,18 +3455,18 @@
         <v>60</v>
       </c>
       <c r="H35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I35" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s">
         <v>58</v>
@@ -3244,7 +3478,7 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
@@ -3253,18 +3487,18 @@
         <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s">
         <v>58</v>
@@ -3276,7 +3510,7 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
@@ -3285,18 +3519,18 @@
         <v>60</v>
       </c>
       <c r="H37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B38" t="s">
         <v>90</v>
@@ -3308,7 +3542,7 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
@@ -3317,18 +3551,18 @@
         <v>60</v>
       </c>
       <c r="H38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I38" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B39" t="s">
         <v>116</v>
@@ -3340,7 +3574,7 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
@@ -3349,21 +3583,21 @@
         <v>60</v>
       </c>
       <c r="H39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -3372,7 +3606,7 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
@@ -3381,18 +3615,18 @@
         <v>60</v>
       </c>
       <c r="H40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B41" t="s">
         <v>58</v>
@@ -3404,7 +3638,7 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
@@ -3413,18 +3647,18 @@
         <v>60</v>
       </c>
       <c r="H41" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J41" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s">
         <v>58</v>
@@ -3436,7 +3670,7 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
@@ -3445,18 +3679,18 @@
         <v>60</v>
       </c>
       <c r="H42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
@@ -3468,7 +3702,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
@@ -3477,21 +3711,21 @@
         <v>60</v>
       </c>
       <c r="H43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -3500,7 +3734,7 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
@@ -3509,18 +3743,18 @@
         <v>60</v>
       </c>
       <c r="H44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I44" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B45" t="s">
         <v>58</v>
@@ -3532,7 +3766,7 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
@@ -3541,18 +3775,18 @@
         <v>60</v>
       </c>
       <c r="H45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B46" t="s">
         <v>58</v>
@@ -3564,7 +3798,7 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
@@ -3573,18 +3807,18 @@
         <v>60</v>
       </c>
       <c r="H46" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B47" t="s">
         <v>90</v>
@@ -3596,7 +3830,7 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
@@ -3605,18 +3839,18 @@
         <v>60</v>
       </c>
       <c r="H47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J47" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B48" t="s">
         <v>58</v>
@@ -3628,7 +3862,7 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
@@ -3637,18 +3871,18 @@
         <v>60</v>
       </c>
       <c r="H48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J48" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B49" t="s">
         <v>58</v>
@@ -3660,7 +3894,7 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
@@ -3669,21 +3903,21 @@
         <v>60</v>
       </c>
       <c r="H49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -3692,7 +3926,7 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
@@ -3701,18 +3935,18 @@
         <v>60</v>
       </c>
       <c r="H50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B51" t="s">
         <v>58</v>
@@ -3724,7 +3958,7 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
@@ -3733,18 +3967,18 @@
         <v>60</v>
       </c>
       <c r="H51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
@@ -3756,7 +3990,7 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
@@ -3765,18 +3999,18 @@
         <v>60</v>
       </c>
       <c r="H52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J52" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B53" t="s">
         <v>58</v>
@@ -3788,7 +4022,7 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
@@ -3797,18 +4031,18 @@
         <v>60</v>
       </c>
       <c r="H53" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J53" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B54" t="s">
         <v>116</v>
@@ -3820,7 +4054,7 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
@@ -3829,18 +4063,18 @@
         <v>60</v>
       </c>
       <c r="H54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I54" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J54" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
@@ -3852,7 +4086,7 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
@@ -3861,18 +4095,18 @@
         <v>60</v>
       </c>
       <c r="H55" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I55" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J55" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B56" t="s">
         <v>58</v>
@@ -3884,7 +4118,7 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
@@ -3893,18 +4127,18 @@
         <v>60</v>
       </c>
       <c r="H56" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I56" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J56" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B57" t="s">
         <v>58</v>
@@ -3916,7 +4150,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
@@ -3925,18 +4159,18 @@
         <v>60</v>
       </c>
       <c r="H57" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I57" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J57" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B58" t="s">
         <v>58</v>
@@ -3948,7 +4182,7 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
@@ -3957,18 +4191,18 @@
         <v>60</v>
       </c>
       <c r="H58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I58" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J58" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B59" t="s">
         <v>58</v>
@@ -3980,7 +4214,7 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
@@ -3989,18 +4223,18 @@
         <v>60</v>
       </c>
       <c r="H59" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B60" t="s">
         <v>58</v>
@@ -4012,7 +4246,7 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
@@ -4021,18 +4255,18 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J60" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B61" t="s">
         <v>58</v>
@@ -4044,7 +4278,7 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
@@ -4053,18 +4287,18 @@
         <v>60</v>
       </c>
       <c r="H61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J61" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B62" t="s">
         <v>90</v>
@@ -4076,7 +4310,7 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F62" t="s">
         <v>14</v>
@@ -4085,18 +4319,18 @@
         <v>60</v>
       </c>
       <c r="H62" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I62" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J62" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B63" t="s">
         <v>58</v>
@@ -4108,7 +4342,7 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
@@ -4117,18 +4351,18 @@
         <v>60</v>
       </c>
       <c r="H63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I63" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J63" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B64" t="s">
         <v>90</v>
@@ -4140,7 +4374,7 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
@@ -4149,18 +4383,18 @@
         <v>60</v>
       </c>
       <c r="H64" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I64" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J64" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B65" t="s">
         <v>58</v>
@@ -4172,7 +4406,7 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F65" t="s">
         <v>14</v>
@@ -4181,18 +4415,18 @@
         <v>60</v>
       </c>
       <c r="H65" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I65" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B66" t="s">
         <v>58</v>
@@ -4204,7 +4438,7 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F66" t="s">
         <v>14</v>
@@ -4213,18 +4447,18 @@
         <v>60</v>
       </c>
       <c r="H66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I66" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B67" t="s">
         <v>58</v>
@@ -4236,7 +4470,7 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
@@ -4245,21 +4479,21 @@
         <v>60</v>
       </c>
       <c r="H67" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I67" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J67" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B68" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -4268,7 +4502,7 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
@@ -4277,21 +4511,21 @@
         <v>60</v>
       </c>
       <c r="H68" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I68" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J68" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B69" t="s">
-        <v>116</v>
+        <v>367</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
@@ -4300,7 +4534,7 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F69" t="s">
         <v>14</v>
@@ -4309,21 +4543,21 @@
         <v>60</v>
       </c>
       <c r="H69" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I69" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J69" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B70" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -4332,7 +4566,7 @@
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
@@ -4341,18 +4575,18 @@
         <v>60</v>
       </c>
       <c r="H70" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I70" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J70" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B71" t="s">
         <v>90</v>
@@ -4364,7 +4598,7 @@
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F71" t="s">
         <v>14</v>
@@ -4373,18 +4607,18 @@
         <v>60</v>
       </c>
       <c r="H71" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I71" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J71" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B72" t="s">
         <v>58</v>
@@ -4396,7 +4630,7 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F72" t="s">
         <v>14</v>
@@ -4405,18 +4639,18 @@
         <v>60</v>
       </c>
       <c r="H72" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I72" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J72" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B73" t="s">
         <v>58</v>
@@ -4428,7 +4662,7 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F73" t="s">
         <v>14</v>
@@ -4437,18 +4671,18 @@
         <v>60</v>
       </c>
       <c r="H73" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I73" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J73" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B74" t="s">
         <v>58</v>
@@ -4460,7 +4694,7 @@
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F74" t="s">
         <v>14</v>
@@ -4469,18 +4703,18 @@
         <v>60</v>
       </c>
       <c r="H74" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I74" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J74" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B75" t="s">
         <v>58</v>
@@ -4492,7 +4726,7 @@
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F75" t="s">
         <v>14</v>
@@ -4501,18 +4735,18 @@
         <v>60</v>
       </c>
       <c r="H75" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I75" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J75" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B76" t="s">
         <v>58</v>
@@ -4524,7 +4758,7 @@
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F76" t="s">
         <v>14</v>
@@ -4533,21 +4767,21 @@
         <v>60</v>
       </c>
       <c r="H76" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I76" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J76" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B77" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C77" t="s">
         <v>12</v>
@@ -4556,7 +4790,7 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F77" t="s">
         <v>14</v>
@@ -4565,21 +4799,21 @@
         <v>47</v>
       </c>
       <c r="H77" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I77" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J77" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B78" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
@@ -4588,7 +4822,7 @@
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
@@ -4597,21 +4831,21 @@
         <v>28</v>
       </c>
       <c r="H78" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I78" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J78" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B79" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
@@ -4620,7 +4854,7 @@
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F79" t="s">
         <v>14</v>
@@ -4629,21 +4863,21 @@
         <v>28</v>
       </c>
       <c r="H79" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I79" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J79" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B80" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C80" t="s">
         <v>12</v>
@@ -4652,30 +4886,30 @@
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F80" t="s">
         <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H80" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I80" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J80" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B81" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C81" t="s">
         <v>12</v>
@@ -4684,30 +4918,30 @@
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F81" t="s">
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
       <c r="H81" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I81" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J81" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B82" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C82" t="s">
         <v>12</v>
@@ -4716,30 +4950,30 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F82" t="s">
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
       <c r="H82" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I82" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J82" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B83" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="C83" t="s">
         <v>12</v>
@@ -4748,30 +4982,30 @@
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F83" t="s">
         <v>14</v>
       </c>
       <c r="G83" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
       <c r="H83" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="I83" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="J83" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B84" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C84" t="s">
         <v>12</v>
@@ -4780,30 +5014,30 @@
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F84" t="s">
         <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>28</v>
+        <v>429</v>
       </c>
       <c r="H84" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="I84" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J84" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B85" t="s">
-        <v>455</v>
+        <v>373</v>
       </c>
       <c r="C85" t="s">
         <v>12</v>
@@ -4812,30 +5046,30 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F85" t="s">
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H85" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I85" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J85" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B86" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C86" t="s">
         <v>12</v>
@@ -4844,30 +5078,30 @@
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F86" t="s">
         <v>14</v>
       </c>
       <c r="G86" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
       <c r="H86" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I86" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J86" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B87" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C87" t="s">
         <v>12</v>
@@ -4876,30 +5110,30 @@
         <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F87" t="s">
         <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
       <c r="H87" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I87" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J87" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B88" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C88" t="s">
         <v>12</v>
@@ -4914,88 +5148,88 @@
         <v>14</v>
       </c>
       <c r="G88" t="s">
+        <v>429</v>
+      </c>
+      <c r="H88" t="s">
         <v>475</v>
       </c>
-      <c r="H88" t="s">
+      <c r="I88" t="s">
         <v>476</v>
       </c>
-      <c r="I88" t="s">
+      <c r="J88" t="s">
         <v>477</v>
-      </c>
-      <c r="J88" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>478</v>
+      </c>
+      <c r="B89" t="s">
         <v>479</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" t="s">
         <v>480</v>
       </c>
-      <c r="C89" t="s">
-        <v>12</v>
-      </c>
-      <c r="D89" t="s">
-        <v>12</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" t="s">
+        <v>429</v>
+      </c>
+      <c r="H89" t="s">
         <v>481</v>
       </c>
-      <c r="F89" t="s">
-        <v>14</v>
-      </c>
-      <c r="G89" t="s">
-        <v>47</v>
-      </c>
-      <c r="H89" t="s">
+      <c r="I89" t="s">
         <v>482</v>
       </c>
-      <c r="I89" t="s">
+      <c r="J89" t="s">
         <v>483</v>
-      </c>
-      <c r="J89" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>484</v>
+      </c>
+      <c r="B90" t="s">
         <v>485</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" t="s">
         <v>486</v>
       </c>
-      <c r="C90" t="s">
-        <v>12</v>
-      </c>
-      <c r="D90" t="s">
-        <v>12</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" t="s">
+        <v>429</v>
+      </c>
+      <c r="H90" t="s">
         <v>487</v>
       </c>
-      <c r="F90" t="s">
-        <v>14</v>
-      </c>
-      <c r="G90" t="s">
-        <v>47</v>
-      </c>
-      <c r="H90" t="s">
+      <c r="I90" t="s">
         <v>488</v>
       </c>
-      <c r="I90" t="s">
+      <c r="J90" t="s">
         <v>489</v>
-      </c>
-      <c r="J90" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>490</v>
+      </c>
+      <c r="B91" t="s">
         <v>491</v>
-      </c>
-      <c r="B91" t="s">
-        <v>137</v>
       </c>
       <c r="C91" t="s">
         <v>12</v>
@@ -5010,7 +5244,7 @@
         <v>14</v>
       </c>
       <c r="G91" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
       <c r="H91" t="s">
         <v>493</v>
@@ -5027,7 +5261,7 @@
         <v>496</v>
       </c>
       <c r="B92" t="s">
-        <v>218</v>
+        <v>497</v>
       </c>
       <c r="C92" t="s">
         <v>12</v>
@@ -5036,13 +5270,13 @@
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F92" t="s">
         <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>498</v>
+        <v>429</v>
       </c>
       <c r="H92" t="s">
         <v>499</v>
@@ -5059,7 +5293,7 @@
         <v>502</v>
       </c>
       <c r="B93" t="s">
-        <v>371</v>
+        <v>503</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
@@ -5068,30 +5302,30 @@
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F93" t="s">
         <v>14</v>
       </c>
       <c r="G93" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H93" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I93" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J93" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B94" t="s">
-        <v>218</v>
+        <v>510</v>
       </c>
       <c r="C94" t="s">
         <v>12</v>
@@ -5100,30 +5334,30 @@
         <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F94" t="s">
         <v>14</v>
       </c>
       <c r="G94" t="s">
-        <v>498</v>
+        <v>47</v>
       </c>
       <c r="H94" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I94" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J94" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B95" t="s">
-        <v>371</v>
+        <v>516</v>
       </c>
       <c r="C95" t="s">
         <v>12</v>
@@ -5132,30 +5366,30 @@
         <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F95" t="s">
         <v>14</v>
       </c>
       <c r="G95" t="s">
-        <v>504</v>
+        <v>47</v>
       </c>
       <c r="H95" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="I95" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J95" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B96" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="C96" t="s">
         <v>12</v>
@@ -5164,51 +5398,51 @@
         <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F96" t="s">
         <v>14</v>
       </c>
       <c r="G96" t="s">
-        <v>521</v>
+        <v>47</v>
       </c>
       <c r="H96" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I96" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J96" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>527</v>
       </c>
       <c r="C97" t="s">
-        <v>526</v>
+        <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>527</v>
+        <v>12</v>
       </c>
       <c r="E97" t="s">
         <v>528</v>
       </c>
       <c r="F97" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" t="s">
+        <v>28</v>
+      </c>
+      <c r="H97" t="s">
         <v>529</v>
       </c>
-      <c r="G97" t="s">
-        <v>12</v>
-      </c>
-      <c r="H97" t="s">
+      <c r="I97" t="s">
         <v>530</v>
-      </c>
-      <c r="I97" t="s">
-        <v>12</v>
       </c>
       <c r="J97" t="s">
         <v>531</v>
@@ -5234,7 +5468,7 @@
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="H98" t="s">
         <v>535</v>
@@ -5251,7 +5485,7 @@
         <v>538</v>
       </c>
       <c r="B99" t="s">
-        <v>218</v>
+        <v>539</v>
       </c>
       <c r="C99" t="s">
         <v>12</v>
@@ -5260,30 +5494,30 @@
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F99" t="s">
         <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>498</v>
+        <v>47</v>
       </c>
       <c r="H99" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I99" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="J99" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B100" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C100" t="s">
         <v>12</v>
@@ -5292,30 +5526,30 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F100" t="s">
         <v>14</v>
       </c>
       <c r="G100" t="s">
-        <v>521</v>
+        <v>47</v>
       </c>
       <c r="H100" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I100" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J100" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B101" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C101" t="s">
         <v>12</v>
@@ -5324,30 +5558,30 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="F101" t="s">
         <v>14</v>
       </c>
       <c r="G101" t="s">
-        <v>521</v>
+        <v>553</v>
       </c>
       <c r="H101" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="I101" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="J101" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B102" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C102" t="s">
         <v>12</v>
@@ -5356,30 +5590,30 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F102" t="s">
         <v>14</v>
       </c>
       <c r="G102" t="s">
-        <v>521</v>
+        <v>47</v>
       </c>
       <c r="H102" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="I102" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="J102" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B103" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C103" t="s">
         <v>12</v>
@@ -5388,22 +5622,438 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F103" t="s">
         <v>14</v>
       </c>
       <c r="G103" t="s">
-        <v>521</v>
+        <v>47</v>
       </c>
       <c r="H103" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="I103" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J103" t="s">
-        <v>565</v>
+        <v>568</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>569</v>
+      </c>
+      <c r="B104" t="s">
+        <v>137</v>
+      </c>
+      <c r="C104" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" t="s">
+        <v>570</v>
+      </c>
+      <c r="F104" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" t="s">
+        <v>47</v>
+      </c>
+      <c r="H104" t="s">
+        <v>571</v>
+      </c>
+      <c r="I104" t="s">
+        <v>572</v>
+      </c>
+      <c r="J104" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>574</v>
+      </c>
+      <c r="B105" t="s">
+        <v>219</v>
+      </c>
+      <c r="C105" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" t="s">
+        <v>12</v>
+      </c>
+      <c r="E105" t="s">
+        <v>575</v>
+      </c>
+      <c r="F105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>576</v>
+      </c>
+      <c r="H105" t="s">
+        <v>577</v>
+      </c>
+      <c r="I105" t="s">
+        <v>578</v>
+      </c>
+      <c r="J105" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>580</v>
+      </c>
+      <c r="B106" t="s">
+        <v>373</v>
+      </c>
+      <c r="C106" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" t="s">
+        <v>581</v>
+      </c>
+      <c r="F106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s">
+        <v>582</v>
+      </c>
+      <c r="H106" t="s">
+        <v>583</v>
+      </c>
+      <c r="I106" t="s">
+        <v>584</v>
+      </c>
+      <c r="J106" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>586</v>
+      </c>
+      <c r="B107" t="s">
+        <v>219</v>
+      </c>
+      <c r="C107" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107" t="s">
+        <v>587</v>
+      </c>
+      <c r="F107" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>576</v>
+      </c>
+      <c r="H107" t="s">
+        <v>588</v>
+      </c>
+      <c r="I107" t="s">
+        <v>589</v>
+      </c>
+      <c r="J107" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>591</v>
+      </c>
+      <c r="B108" t="s">
+        <v>373</v>
+      </c>
+      <c r="C108" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" t="s">
+        <v>592</v>
+      </c>
+      <c r="F108" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>582</v>
+      </c>
+      <c r="H108" t="s">
+        <v>593</v>
+      </c>
+      <c r="I108" t="s">
+        <v>594</v>
+      </c>
+      <c r="J108" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>596</v>
+      </c>
+      <c r="B109" t="s">
+        <v>597</v>
+      </c>
+      <c r="C109" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" t="s">
+        <v>12</v>
+      </c>
+      <c r="E109" t="s">
+        <v>598</v>
+      </c>
+      <c r="F109" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>599</v>
+      </c>
+      <c r="H109" t="s">
+        <v>600</v>
+      </c>
+      <c r="I109" t="s">
+        <v>601</v>
+      </c>
+      <c r="J109" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>603</v>
+      </c>
+      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" t="s">
+        <v>604</v>
+      </c>
+      <c r="D110" t="s">
+        <v>605</v>
+      </c>
+      <c r="E110" t="s">
+        <v>606</v>
+      </c>
+      <c r="F110" t="s">
+        <v>607</v>
+      </c>
+      <c r="G110" t="s">
+        <v>12</v>
+      </c>
+      <c r="H110" t="s">
+        <v>608</v>
+      </c>
+      <c r="I110" t="s">
+        <v>12</v>
+      </c>
+      <c r="J110" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>610</v>
+      </c>
+      <c r="B111" t="s">
+        <v>611</v>
+      </c>
+      <c r="C111" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111" t="s">
+        <v>612</v>
+      </c>
+      <c r="F111" t="s">
+        <v>14</v>
+      </c>
+      <c r="G111" t="s">
+        <v>599</v>
+      </c>
+      <c r="H111" t="s">
+        <v>613</v>
+      </c>
+      <c r="I111" t="s">
+        <v>614</v>
+      </c>
+      <c r="J111" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>616</v>
+      </c>
+      <c r="B112" t="s">
+        <v>219</v>
+      </c>
+      <c r="C112" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" t="s">
+        <v>617</v>
+      </c>
+      <c r="F112" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112" t="s">
+        <v>576</v>
+      </c>
+      <c r="H112" t="s">
+        <v>618</v>
+      </c>
+      <c r="I112" t="s">
+        <v>578</v>
+      </c>
+      <c r="J112" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>620</v>
+      </c>
+      <c r="B113" t="s">
+        <v>621</v>
+      </c>
+      <c r="C113" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" t="s">
+        <v>622</v>
+      </c>
+      <c r="F113" t="s">
+        <v>14</v>
+      </c>
+      <c r="G113" t="s">
+        <v>599</v>
+      </c>
+      <c r="H113" t="s">
+        <v>623</v>
+      </c>
+      <c r="I113" t="s">
+        <v>624</v>
+      </c>
+      <c r="J113" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>626</v>
+      </c>
+      <c r="B114" t="s">
+        <v>627</v>
+      </c>
+      <c r="C114" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" t="s">
+        <v>628</v>
+      </c>
+      <c r="F114" t="s">
+        <v>14</v>
+      </c>
+      <c r="G114" t="s">
+        <v>599</v>
+      </c>
+      <c r="H114" t="s">
+        <v>629</v>
+      </c>
+      <c r="I114" t="s">
+        <v>630</v>
+      </c>
+      <c r="J114" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>632</v>
+      </c>
+      <c r="B115" t="s">
+        <v>633</v>
+      </c>
+      <c r="C115" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" t="s">
+        <v>634</v>
+      </c>
+      <c r="F115" t="s">
+        <v>14</v>
+      </c>
+      <c r="G115" t="s">
+        <v>599</v>
+      </c>
+      <c r="H115" t="s">
+        <v>635</v>
+      </c>
+      <c r="I115" t="s">
+        <v>636</v>
+      </c>
+      <c r="J115" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>638</v>
+      </c>
+      <c r="B116" t="s">
+        <v>639</v>
+      </c>
+      <c r="C116" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" t="s">
+        <v>640</v>
+      </c>
+      <c r="F116" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116" t="s">
+        <v>599</v>
+      </c>
+      <c r="H116" t="s">
+        <v>641</v>
+      </c>
+      <c r="I116" t="s">
+        <v>642</v>
+      </c>
+      <c r="J116" t="s">
+        <v>643</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-customer-story-page.report.xlsx
+++ b/tools/importer/reports/import-customer-story-page.report.xlsx
@@ -1138,7 +1138,7 @@
     <t>en-us/lp/dt/customer-stories-theguthrieclinic</t>
   </si>
   <si>
-    <t>2026-03-22T03:16:19.503Z</t>
+    <t>2026-03-22T06:55:13.319Z</t>
   </si>
   <si>
     <t>The Guthrie Clinic | Dell USA</t>
